--- a/exports/trend_1d/TATASTEEL_full_report.xlsx
+++ b/exports/trend_1d/TATASTEEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>10.1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42040</v>
+        <v>42041</v>
       </c>
       <c r="H2" t="n">
-        <v>33.52</v>
+        <v>32.49</v>
       </c>
       <c r="I2" t="n">
         <v>32.6616707649</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.59</v>
+        <v>-4.61</v>
       </c>
       <c r="L2" t="n">
-        <v>3.61</v>
+        <v>5.02</v>
       </c>
       <c r="M2" t="n">
         <v>0.73</v>
       </c>
       <c r="N2" t="n">
-        <v>2.84</v>
+        <v>3.07</v>
       </c>
       <c r="O2" t="n">
         <v>2.22</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.06</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42102</v>
+        <v>42103</v>
       </c>
       <c r="H3" t="n">
-        <v>29.32</v>
+        <v>30.29</v>
       </c>
       <c r="I3" t="n">
         <v>30.16474900939182</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K3" t="n">
-        <v>9.76</v>
+        <v>6.77</v>
       </c>
       <c r="L3" t="n">
         <v>4.06</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>11.58</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42146</v>
+        <v>42149</v>
       </c>
       <c r="H4" t="n">
-        <v>29.85</v>
+        <v>28.93</v>
       </c>
       <c r="I4" t="n">
         <v>29.60696799580687</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.45</v>
+        <v>-4.49</v>
       </c>
       <c r="L4" t="n">
-        <v>4.03</v>
+        <v>4.82</v>
       </c>
       <c r="M4" t="n">
         <v>3.55</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.4</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42283</v>
+        <v>42284</v>
       </c>
       <c r="H5" t="n">
-        <v>18.71</v>
+        <v>19.64</v>
       </c>
       <c r="I5" t="n">
         <v>19.35823799346605</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K5" t="n">
-        <v>35.33</v>
+        <v>32.11</v>
       </c>
       <c r="L5" t="n">
         <v>2.7</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>18.84</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42313</v>
+        <v>42314</v>
       </c>
       <c r="H6" t="n">
-        <v>18.52</v>
+        <v>17.98</v>
       </c>
       <c r="I6" t="n">
         <v>18.48386119773625</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.7</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>6.72</v>
+        <v>10.95</v>
       </c>
       <c r="M6" t="n">
-        <v>1.38</v>
+        <v>3.46</v>
       </c>
       <c r="N6" t="n">
         <v>5.03</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>13.38</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42339</v>
+        <v>42340</v>
       </c>
       <c r="H7" t="n">
-        <v>19.69</v>
+        <v>20.33</v>
       </c>
       <c r="I7" t="n">
         <v>20.3243683124949</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.51</v>
+        <v>-13.07</v>
       </c>
       <c r="L7" t="n">
-        <v>10.07</v>
+        <v>14.13</v>
       </c>
       <c r="M7" t="n">
         <v>1.35</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>11.53</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42382</v>
+        <v>42383</v>
       </c>
       <c r="H8" t="n">
-        <v>20.57</v>
+        <v>19.79</v>
       </c>
       <c r="I8" t="n">
         <v>20.3796304614232</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K8" t="n">
-        <v>1.18</v>
+        <v>-2.66</v>
       </c>
       <c r="L8" t="n">
         <v>9.15</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>5.44</v>
       </c>
       <c r="N8" t="n">
         <v>7.97</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>15.27</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H9" t="n">
-        <v>21.6</v>
+        <v>22.62</v>
       </c>
       <c r="I9" t="n">
         <v>21.67275114175118</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.15</v>
+        <v>-14.3</v>
       </c>
       <c r="L9" t="n">
-        <v>12.33</v>
+        <v>15.31</v>
       </c>
       <c r="M9" t="n">
         <v>2.48</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>16.46</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42502</v>
+        <v>42503</v>
       </c>
       <c r="H10" t="n">
-        <v>28.78</v>
+        <v>28</v>
       </c>
       <c r="I10" t="n">
         <v>28.06871953907674</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K10" t="n">
-        <v>27.23</v>
+        <v>23.78</v>
       </c>
       <c r="L10" t="n">
         <v>3.45</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.21</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42562</v>
+        <v>42563</v>
       </c>
       <c r="H11" t="n">
-        <v>28.44</v>
+        <v>29.95</v>
       </c>
       <c r="I11" t="n">
         <v>29.94192939430916</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.57</v>
+        <v>-6.96</v>
       </c>
       <c r="L11" t="n">
         <v>9.07</v>
@@ -1068,7 +1199,7 @@
         <v>2.28</v>
       </c>
       <c r="N11" t="n">
-        <v>4.18</v>
+        <v>5.31</v>
       </c>
       <c r="O11" t="n">
         <v>-2.71</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.78</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42627</v>
+        <v>42628</v>
       </c>
       <c r="H12" t="n">
-        <v>33.03</v>
+        <v>32.3</v>
       </c>
       <c r="I12" t="n">
         <v>32.40144362374292</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K12" t="n">
-        <v>10.28</v>
+        <v>7.85</v>
       </c>
       <c r="L12" t="n">
         <v>4.41</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>12.06</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42649</v>
+        <v>42650</v>
       </c>
       <c r="H13" t="n">
-        <v>34.59</v>
+        <v>36.21</v>
       </c>
       <c r="I13" t="n">
         <v>35.20632381415444</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.09</v>
+        <v>-12.11</v>
       </c>
       <c r="L13" t="n">
-        <v>9.07</v>
+        <v>12.38</v>
       </c>
       <c r="M13" t="n">
         <v>2.24</v>
       </c>
       <c r="N13" t="n">
-        <v>3.76</v>
+        <v>4.68</v>
       </c>
       <c r="O13" t="n">
         <v>-2.21</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>11.59</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42669</v>
+        <v>42670</v>
       </c>
       <c r="H14" t="n">
-        <v>35.42</v>
+        <v>35.28</v>
       </c>
       <c r="I14" t="n">
         <v>35.410207771791</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.18</v>
+        <v>-2.57</v>
       </c>
       <c r="L14" t="n">
-        <v>4.47</v>
+        <v>6.21</v>
       </c>
       <c r="M14" t="n">
         <v>4.09</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H15" t="n">
-        <v>35.52</v>
+        <v>39.19</v>
       </c>
       <c r="I15" t="n">
         <v>38.53185853436436</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.68</v>
+        <v>-11.08</v>
       </c>
       <c r="L15" t="n">
-        <v>7.48</v>
+        <v>11.76</v>
       </c>
       <c r="M15" t="n">
-        <v>0.98</v>
+        <v>2.34</v>
       </c>
       <c r="N15" t="n">
-        <v>3.24</v>
+        <v>10.33</v>
       </c>
       <c r="O15" t="n">
         <v>-0.4</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>16.43</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42692</v>
+        <v>42695</v>
       </c>
       <c r="H16" t="n">
-        <v>34.1</v>
+        <v>32.79</v>
       </c>
       <c r="I16" t="n">
         <v>33.63724152257947</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>-12.99</v>
+        <v>-16.33</v>
       </c>
       <c r="L16" t="n">
-        <v>13.98</v>
+        <v>17.58</v>
       </c>
       <c r="M16" t="n">
         <v>3.85</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>20.01</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H17" t="n">
-        <v>36.11</v>
+        <v>37.48</v>
       </c>
       <c r="I17" t="n">
         <v>37.45169617522021</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.13</v>
+        <v>-14.3</v>
       </c>
       <c r="L17" t="n">
         <v>19.06</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.25</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42837</v>
+        <v>42838</v>
       </c>
       <c r="H18" t="n">
-        <v>43.14</v>
+        <v>41.78</v>
       </c>
       <c r="I18" t="n">
         <v>41.95971276864069</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K18" t="n">
-        <v>15.1</v>
+        <v>11.47</v>
       </c>
       <c r="L18" t="n">
         <v>3.15</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>10.31</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42871</v>
+        <v>42872</v>
       </c>
       <c r="H19" t="n">
-        <v>41.09</v>
+        <v>44.76</v>
       </c>
       <c r="I19" t="n">
         <v>42.15410550261745</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K19" t="n">
-        <v>1.65</v>
+        <v>-7.13</v>
       </c>
       <c r="L19" t="n">
-        <v>3.61</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>1.68</v>
+        <v>3.21</v>
       </c>
       <c r="N19" t="n">
-        <v>4.85</v>
+        <v>8.93</v>
       </c>
       <c r="O19" t="n">
         <v>-3.15</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.97</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H20" t="n">
-        <v>60.39</v>
+        <v>58.97</v>
       </c>
       <c r="I20" t="n">
         <v>59.9285553943807</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K20" t="n">
-        <v>34.92</v>
+        <v>31.75</v>
       </c>
       <c r="L20" t="n">
         <v>6.12</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>8.4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43013</v>
+        <v>43014</v>
       </c>
       <c r="H21" t="n">
-        <v>61.08</v>
+        <v>64.06</v>
       </c>
       <c r="I21" t="n">
         <v>63.92192013055163</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.58</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>4.39</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>0.98</v>
       </c>
       <c r="N21" t="n">
-        <v>2.41</v>
+        <v>4.88</v>
       </c>
       <c r="O21" t="n">
         <v>-2.35</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>9.18</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H22" t="n">
-        <v>63.47</v>
+        <v>62.69</v>
       </c>
       <c r="I22" t="n">
         <v>63.2785947119816</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.92</v>
+        <v>-2.14</v>
       </c>
       <c r="L22" t="n">
         <v>4.04</v>
       </c>
       <c r="M22" t="n">
-        <v>0.59</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
         <v>2.09</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.13</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H23" t="n">
-        <v>65.18000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="I23" t="n">
         <v>65.98945921285858</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.97</v>
+        <v>-5.76</v>
       </c>
       <c r="L23" t="n">
         <v>6.38</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43130</v>
+        <v>43131</v>
       </c>
       <c r="H24" t="n">
-        <v>72.31</v>
+        <v>65.38</v>
       </c>
       <c r="I24" t="n">
         <v>68.07947297853225</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>9.06</v>
+        <v>-1.39</v>
       </c>
       <c r="L24" t="n">
         <v>1.99</v>
       </c>
       <c r="M24" t="n">
-        <v>0.34</v>
+        <v>5.46</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>9.58</v>
       </c>
       <c r="O24" t="n">
         <v>1.72</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>14.09</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43311</v>
+        <v>43312</v>
       </c>
       <c r="H25" t="n">
-        <v>50.52</v>
+        <v>51.5</v>
       </c>
       <c r="I25" t="n">
         <v>51.07088986347253</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K25" t="n">
-        <v>22.73</v>
+        <v>21.23</v>
       </c>
       <c r="L25" t="n">
         <v>6.42</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>7</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.45</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43377</v>
+        <v>43378</v>
       </c>
       <c r="H26" t="n">
-        <v>53.4</v>
+        <v>51.99</v>
       </c>
       <c r="I26" t="n">
         <v>52.28060309932918</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K26" t="n">
-        <v>3.69</v>
+        <v>0.95</v>
       </c>
       <c r="L26" t="n">
         <v>4.27</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>14.21</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H27" t="n">
-        <v>41.87</v>
+        <v>43.88</v>
       </c>
       <c r="I27" t="n">
         <v>43.44778826978342</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K27" t="n">
-        <v>19.47</v>
+        <v>15.6</v>
       </c>
       <c r="L27" t="n">
         <v>7.98</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.36</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43579</v>
+        <v>43580</v>
       </c>
       <c r="H28" t="n">
-        <v>47.79</v>
+        <v>46.37</v>
       </c>
       <c r="I28" t="n">
         <v>46.43377343083527</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K28" t="n">
-        <v>8.91</v>
+        <v>5.67</v>
       </c>
       <c r="L28" t="n">
         <v>5.47</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.43</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43765</v>
+        <v>43767</v>
       </c>
       <c r="H29" t="n">
-        <v>32.15</v>
+        <v>34.59</v>
       </c>
       <c r="I29" t="n">
         <v>33.5015382220813</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K29" t="n">
-        <v>30.67</v>
+        <v>25.4</v>
       </c>
       <c r="L29" t="n">
         <v>10.74</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>14.64</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43854</v>
+        <v>43857</v>
       </c>
       <c r="H30" t="n">
-        <v>43.73</v>
+        <v>41.68</v>
       </c>
       <c r="I30" t="n">
         <v>41.9233003279233</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K30" t="n">
-        <v>26.42</v>
+        <v>20.5</v>
       </c>
       <c r="L30" t="n">
         <v>6.91</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>10.1</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43865</v>
+        <v>43866</v>
       </c>
       <c r="H31" t="n">
-        <v>40.65</v>
+        <v>42.9</v>
       </c>
       <c r="I31" t="n">
         <v>42.66990042644115</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
-        <v>2.47</v>
+        <v>-2.93</v>
       </c>
       <c r="L31" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="M31" t="n">
         <v>1.7</v>
       </c>
       <c r="N31" t="n">
-        <v>3.99</v>
+        <v>5.54</v>
       </c>
       <c r="O31" t="n">
         <v>-4.69</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>14.28</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43881</v>
+        <v>43885</v>
       </c>
       <c r="H32" t="n">
-        <v>39.82</v>
+        <v>37.09</v>
       </c>
       <c r="I32" t="n">
         <v>38.33710833021196</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>-7.18</v>
+        <v>-13.54</v>
       </c>
       <c r="L32" t="n">
-        <v>12.19</v>
+        <v>14.01</v>
       </c>
       <c r="M32" t="n">
         <v>2.54</v>
       </c>
       <c r="N32" t="n">
-        <v>6.21</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
         <v>5.54</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>15.51</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H33" t="n">
-        <v>25.31</v>
+        <v>27.26</v>
       </c>
       <c r="I33" t="n">
         <v>26.66717469122302</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K33" t="n">
-        <v>31.76</v>
+        <v>26.5</v>
       </c>
       <c r="L33" t="n">
         <v>5.12</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>15.57</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44090</v>
+        <v>44091</v>
       </c>
       <c r="H34" t="n">
-        <v>36.01</v>
+        <v>35.42</v>
       </c>
       <c r="I34" t="n">
         <v>35.55050210631738</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K34" t="n">
-        <v>32.1</v>
+        <v>29.93</v>
       </c>
       <c r="L34" t="n">
         <v>5.36</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>12.4</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44124</v>
+        <v>44125</v>
       </c>
       <c r="H35" t="n">
-        <v>34.84</v>
+        <v>35.96</v>
       </c>
       <c r="I35" t="n">
         <v>35.4324794758988</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K35" t="n">
-        <v>1.64</v>
+        <v>-1.52</v>
       </c>
       <c r="L35" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="M35" t="n">
         <v>2.53</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.98</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H36" t="n">
-        <v>60.2</v>
+        <v>57.66</v>
       </c>
       <c r="I36" t="n">
         <v>59.1522007614906</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K36" t="n">
-        <v>67.41</v>
+        <v>60.34</v>
       </c>
       <c r="L36" t="n">
         <v>2.59</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>16.72</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44232</v>
+        <v>44235</v>
       </c>
       <c r="H37" t="n">
-        <v>63.42</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I37" t="n">
         <v>65.07522380293435</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.99</v>
+        <v>-13.04</v>
       </c>
       <c r="L37" t="n">
-        <v>10.93</v>
+        <v>13.39</v>
       </c>
       <c r="M37" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="N37" t="n">
         <v>6.19</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>14.55</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44428</v>
+        <v>44431</v>
       </c>
       <c r="H38" t="n">
-        <v>130.9</v>
+        <v>129.24</v>
       </c>
       <c r="I38" t="n">
         <v>129.7480612893321</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K38" t="n">
-        <v>100.83</v>
+        <v>98.28</v>
       </c>
       <c r="L38" t="n">
         <v>7.04</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>7</v>
+      </c>
+      <c r="U38" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>13.98</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44573</v>
+        <v>44574</v>
       </c>
       <c r="H39" t="n">
-        <v>108.57</v>
+        <v>115.8</v>
       </c>
       <c r="I39" t="n">
         <v>114.0072726910473</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K39" t="n">
-        <v>15.99</v>
+        <v>10.4</v>
       </c>
       <c r="L39" t="n">
         <v>8.880000000000001</v>
@@ -2664,7 +3131,7 @@
         <v>3.21</v>
       </c>
       <c r="N39" t="n">
-        <v>4.19</v>
+        <v>6.66</v>
       </c>
       <c r="O39" t="n">
         <v>-1.27</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>11.72</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H40" t="n">
-        <v>110.77</v>
+        <v>103.88</v>
       </c>
       <c r="I40" t="n">
         <v>105.3564333026428</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.34</v>
+        <v>-10.29</v>
       </c>
       <c r="L40" t="n">
-        <v>5.82</v>
+        <v>11.05</v>
       </c>
       <c r="M40" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="N40" t="n">
-        <v>3.16</v>
+        <v>6.22</v>
       </c>
       <c r="O40" t="n">
         <v>6.66</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>14.34</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44599</v>
+        <v>44600</v>
       </c>
       <c r="H41" t="n">
-        <v>112.09</v>
+        <v>115.65</v>
       </c>
       <c r="I41" t="n">
         <v>114.4247074634103</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.9</v>
+        <v>-11.33</v>
       </c>
       <c r="L41" t="n">
-        <v>10.86</v>
+        <v>11.62</v>
       </c>
       <c r="M41" t="n">
         <v>2.43</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>12.91</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H42" t="n">
-        <v>107.79</v>
+        <v>101.43</v>
       </c>
       <c r="I42" t="n">
         <v>106.8675128401527</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.8</v>
+        <v>-12.3</v>
       </c>
       <c r="L42" t="n">
-        <v>8.49</v>
+        <v>12.88</v>
       </c>
       <c r="M42" t="n">
-        <v>2.83</v>
+        <v>4.08</v>
       </c>
       <c r="N42" t="n">
-        <v>5.53</v>
+        <v>5.9</v>
       </c>
       <c r="O42" t="n">
         <v>3.18</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>14.02</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44617</v>
+        <v>44620</v>
       </c>
       <c r="H43" t="n">
-        <v>108.42</v>
+        <v>115.75</v>
       </c>
       <c r="I43" t="n">
         <v>115.6537544552093</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.89</v>
+        <v>-14.12</v>
       </c>
       <c r="L43" t="n">
-        <v>7.37</v>
+        <v>14.55</v>
       </c>
       <c r="M43" t="n">
         <v>2.27</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>16.46</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H44" t="n">
-        <v>121.32</v>
+        <v>115.75</v>
       </c>
       <c r="I44" t="n">
         <v>119.4443594465512</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K44" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>7.72</v>
       </c>
       <c r="M44" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="N44" t="n">
         <v>5.04</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>12.07</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44764</v>
+        <v>44767</v>
       </c>
       <c r="H45" t="n">
-        <v>87.95</v>
+        <v>90.34</v>
       </c>
       <c r="I45" t="n">
         <v>88.61484674898568</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K45" t="n">
-        <v>24.02</v>
+        <v>21.95</v>
       </c>
       <c r="L45" t="n">
         <v>9.24</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.6</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44820</v>
+        <v>44823</v>
       </c>
       <c r="H46" t="n">
-        <v>99.77</v>
+        <v>97.23</v>
       </c>
       <c r="I46" t="n">
         <v>98.19051584608297</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K46" t="n">
-        <v>10.44</v>
+        <v>7.63</v>
       </c>
       <c r="L46" t="n">
         <v>2.92</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44869</v>
+        <v>44872</v>
       </c>
       <c r="H47" t="n">
-        <v>98.84</v>
+        <v>100.75</v>
       </c>
       <c r="I47" t="n">
         <v>100.3544744719918</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.66</v>
+        <v>-3.62</v>
       </c>
       <c r="L47" t="n">
         <v>4.82</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H48" t="n">
-        <v>101.68</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I48" t="n">
         <v>100.8220216162116</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K48" t="n">
-        <v>0.92</v>
+        <v>-4.32</v>
       </c>
       <c r="L48" t="n">
-        <v>3.06</v>
+        <v>4.61</v>
       </c>
       <c r="M48" t="n">
-        <v>0.88</v>
+        <v>1.58</v>
       </c>
       <c r="N48" t="n">
-        <v>2.58</v>
+        <v>5.19</v>
       </c>
       <c r="O48" t="n">
         <v>1.93</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>11.52</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44925</v>
+        <v>44928</v>
       </c>
       <c r="H49" t="n">
-        <v>106.56</v>
+        <v>113.01</v>
       </c>
       <c r="I49" t="n">
         <v>107.0169190554934</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K49" t="n">
-        <v>-10.54</v>
+        <v>-17.23</v>
       </c>
       <c r="L49" t="n">
-        <v>12.68</v>
+        <v>17.69</v>
       </c>
       <c r="M49" t="n">
         <v>1.62</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>11.83</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44963</v>
+        <v>44964</v>
       </c>
       <c r="H50" t="n">
-        <v>111.26</v>
+        <v>105.39</v>
       </c>
       <c r="I50" t="n">
         <v>108.2516840699041</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.55</v>
+        <v>-6.74</v>
       </c>
       <c r="L50" t="n">
-        <v>4.75</v>
+        <v>7.52</v>
       </c>
       <c r="M50" t="n">
-        <v>0.54</v>
+        <v>4.26</v>
       </c>
       <c r="N50" t="n">
-        <v>2.48</v>
+        <v>5.28</v>
       </c>
       <c r="O50" t="n">
         <v>6.05</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.62</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45044</v>
+        <v>45048</v>
       </c>
       <c r="H51" t="n">
-        <v>101.97</v>
+        <v>104.27</v>
       </c>
       <c r="I51" t="n">
         <v>103.5254177004445</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K51" t="n">
-        <v>3.25</v>
+        <v>1.06</v>
       </c>
       <c r="L51" t="n">
         <v>3.62</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.99</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45064</v>
+        <v>45065</v>
       </c>
       <c r="H52" t="n">
-        <v>99.28</v>
+        <v>98.75</v>
       </c>
       <c r="I52" t="n">
         <v>98.99650345543398</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.79</v>
+        <v>-5.29</v>
       </c>
       <c r="L52" t="n">
-        <v>4.87</v>
+        <v>5.86</v>
       </c>
       <c r="M52" t="n">
         <v>0.47</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.8</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45083</v>
+        <v>45084</v>
       </c>
       <c r="H53" t="n">
-        <v>103</v>
+        <v>105.44</v>
       </c>
       <c r="I53" t="n">
         <v>103.4132869923153</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.3</v>
+        <v>-6.77</v>
       </c>
       <c r="L53" t="n">
-        <v>5.19</v>
+        <v>7.03</v>
       </c>
       <c r="M53" t="n">
         <v>0.63</v>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="O53" t="n">
         <v>-0.53</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.17</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="H54" t="n">
-        <v>111.94</v>
+        <v>109.79</v>
       </c>
       <c r="I54" t="n">
         <v>110.249990111806</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K54" t="n">
-        <v>6.16</v>
+        <v>4.13</v>
       </c>
       <c r="L54" t="n">
         <v>3.15</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>7.11</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45168</v>
+        <v>45169</v>
       </c>
       <c r="H55" t="n">
-        <v>115.8</v>
+        <v>116.58</v>
       </c>
       <c r="I55" t="n">
         <v>116.2108910001791</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.47</v>
+        <v>-6.18</v>
       </c>
       <c r="L55" t="n">
-        <v>6.01</v>
+        <v>6.81</v>
       </c>
       <c r="M55" t="n">
         <v>0.85</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>5.21</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H56" t="n">
-        <v>116.78</v>
+        <v>113.75</v>
       </c>
       <c r="I56" t="n">
         <v>116.7065559442818</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K56" t="n">
-        <v>0.17</v>
+        <v>-2.43</v>
       </c>
       <c r="L56" t="n">
-        <v>0.63</v>
+        <v>2.68</v>
       </c>
       <c r="M56" t="n">
         <v>1.3</v>
       </c>
       <c r="N56" t="n">
-        <v>2.37</v>
+        <v>2.59</v>
       </c>
       <c r="O56" t="n">
         <v>0.67</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H57" t="n">
-        <v>117.71</v>
+        <v>118.34</v>
       </c>
       <c r="I57" t="n">
         <v>118.2336879257046</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.48</v>
+        <v>-4.04</v>
       </c>
       <c r="L57" t="n">
-        <v>3.78</v>
+        <v>4.51</v>
       </c>
       <c r="M57" t="n">
         <v>1.33</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.03</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45308</v>
+        <v>45309</v>
       </c>
       <c r="H58" t="n">
-        <v>125.13</v>
+        <v>124.5</v>
       </c>
       <c r="I58" t="n">
         <v>124.5342092739632</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K58" t="n">
-        <v>5.74</v>
+        <v>5.21</v>
       </c>
       <c r="L58" t="n">
         <v>1.4</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.25</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="H59" t="n">
-        <v>132.02</v>
+        <v>134.81</v>
       </c>
       <c r="I59" t="n">
         <v>133.5293583244602</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.04</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>6.75</v>
+        <v>9.69</v>
       </c>
       <c r="M59" t="n">
         <v>1.25</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.9</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="H60" t="n">
-        <v>135.69</v>
+        <v>134.95</v>
       </c>
       <c r="I60" t="n">
         <v>135.3090910045299</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K60" t="n">
-        <v>0.65</v>
+        <v>0.1</v>
       </c>
       <c r="L60" t="n">
         <v>5.4</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>11.07</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H61" t="n">
-        <v>148.78</v>
+        <v>155.91</v>
       </c>
       <c r="I61" t="n">
         <v>149.8875258027351</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.25</v>
+        <v>-15.53</v>
       </c>
       <c r="L61" t="n">
-        <v>11.08</v>
+        <v>16.08</v>
       </c>
       <c r="M61" t="n">
         <v>1.66</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>11.47</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H62" t="n">
-        <v>166.76</v>
+        <v>151.81</v>
       </c>
       <c r="I62" t="n">
         <v>156.7613305907424</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K62" t="n">
-        <v>6.96</v>
+        <v>-2.63</v>
       </c>
       <c r="L62" t="n">
-        <v>4.16</v>
+        <v>9.4</v>
       </c>
       <c r="M62" t="n">
         <v>1.32</v>
       </c>
       <c r="N62" t="n">
-        <v>5.92</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O62" t="n">
         <v>4.79</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>15.17</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H63" t="n">
-        <v>174.56</v>
+        <v>174.88</v>
       </c>
       <c r="I63" t="n">
         <v>174.8442583695253</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K63" t="n">
-        <v>-14.99</v>
+        <v>-15.2</v>
       </c>
       <c r="L63" t="n">
-        <v>16.04</v>
+        <v>16.19</v>
       </c>
       <c r="M63" t="n">
         <v>2.06</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>10.29</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H64" t="n">
-        <v>162.57</v>
+        <v>154.17</v>
       </c>
       <c r="I64" t="n">
         <v>162.057998552781</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.04</v>
+        <v>-11.84</v>
       </c>
       <c r="L64" t="n">
-        <v>8.109999999999999</v>
+        <v>12.16</v>
       </c>
       <c r="M64" t="n">
         <v>1.39</v>
       </c>
       <c r="N64" t="n">
-        <v>2.22</v>
+        <v>5.17</v>
       </c>
       <c r="O64" t="n">
         <v>0.18</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.05</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45558</v>
+        <v>45559</v>
       </c>
       <c r="H65" t="n">
-        <v>150.48</v>
+        <v>156.87</v>
       </c>
       <c r="I65" t="n">
         <v>153.944935204597</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K65" t="n">
-        <v>2.39</v>
+        <v>-1.75</v>
       </c>
       <c r="L65" t="n">
         <v>7.09</v>
@@ -4146,7 +4925,7 @@
         <v>2.59</v>
       </c>
       <c r="N65" t="n">
-        <v>3.28</v>
+        <v>4.25</v>
       </c>
       <c r="O65" t="n">
         <v>-5.17</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45579</v>
+        <v>45580</v>
       </c>
       <c r="H66" t="n">
-        <v>154.71</v>
+        <v>152.08</v>
       </c>
       <c r="I66" t="n">
         <v>154.1812075379694</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.38</v>
+        <v>-3.05</v>
       </c>
       <c r="L66" t="n">
         <v>3.54</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H67" t="n">
-        <v>128.13</v>
+        <v>131.55</v>
       </c>
       <c r="I67" t="n">
         <v>131.1697916960327</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K67" t="n">
-        <v>15.75</v>
+        <v>13.5</v>
       </c>
       <c r="L67" t="n">
         <v>2.51</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.44</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H68" t="n">
-        <v>150.12</v>
+        <v>137.19</v>
       </c>
       <c r="I68" t="n">
         <v>143.7410339800786</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K68" t="n">
-        <v>14.12</v>
+        <v>4.29</v>
       </c>
       <c r="L68" t="n">
         <v>5.06</v>
@@ -4317,7 +5132,7 @@
         <v>1.96</v>
       </c>
       <c r="N68" t="n">
-        <v>3.09</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O68" t="n">
         <v>2.67</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>13.79</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="H69" t="n">
-        <v>138.84</v>
+        <v>141.15</v>
       </c>
       <c r="I69" t="n">
         <v>141.0035204035373</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.2</v>
+        <v>-2.89</v>
       </c>
       <c r="L69" t="n">
         <v>8.970000000000001</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H70" t="n">
-        <v>157.94</v>
+        <v>153.01</v>
       </c>
       <c r="I70" t="n">
         <v>156.8580631707858</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K70" t="n">
-        <v>11.9</v>
+        <v>8.4</v>
       </c>
       <c r="L70" t="n">
         <v>2.72</v>
@@ -4431,7 +5270,7 @@
         <v>2.02</v>
       </c>
       <c r="N70" t="n">
-        <v>2.25</v>
+        <v>3.12</v>
       </c>
       <c r="O70" t="n">
         <v>1.66</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>7.94</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="H71" t="n">
-        <v>158.39</v>
+        <v>167.85</v>
       </c>
       <c r="I71" t="n">
         <v>163.569328653887</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.52</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>6.37</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M71" t="n">
         <v>1.74</v>
       </c>
       <c r="N71" t="n">
-        <v>4.28</v>
+        <v>5.97</v>
       </c>
       <c r="O71" t="n">
         <v>-3.12</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>9.57</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="H72" t="n">
-        <v>174.26</v>
+        <v>173.17</v>
       </c>
       <c r="I72" t="n">
         <v>173.301190462834</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K72" t="n">
-        <v>3.82</v>
+        <v>3.17</v>
       </c>
       <c r="L72" t="n">
         <v>5.63</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.79</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="H73" t="n">
-        <v>166.38</v>
+        <v>171.89</v>
       </c>
       <c r="I73" t="n">
         <v>171.3107305491932</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K73" t="n">
-        <v>3.92</v>
+        <v>0.74</v>
       </c>
       <c r="L73" t="n">
         <v>1.2</v>
@@ -4602,7 +5477,7 @@
         <v>0.78</v>
       </c>
       <c r="N73" t="n">
-        <v>2.56</v>
+        <v>3.31</v>
       </c>
       <c r="O73" t="n">
         <v>-0.63</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>7.38</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H74" t="n">
-        <v>211.01</v>
+        <v>196.73</v>
       </c>
       <c r="I74" t="n">
         <v>198.1834058712603</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K74" t="n">
-        <v>22.76</v>
+        <v>14.45</v>
       </c>
       <c r="L74" t="n">
         <v>2.61</v>
@@ -4659,7 +5546,7 @@
         <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>4.54</v>
+        <v>6.77</v>
       </c>
       <c r="O74" t="n">
         <v>3.31</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>12.47</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H75" t="n">
-        <v>205.2</v>
+        <v>206.61</v>
       </c>
       <c r="I75" t="n">
         <v>205.2853119513518</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.31</v>
+        <v>-5.02</v>
       </c>
       <c r="L75" t="n">
-        <v>5.83</v>
+        <v>6.24</v>
       </c>
       <c r="M75" t="n">
         <v>4.24</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H76" t="n">
-        <v>206.77</v>
+        <v>202.72</v>
       </c>
       <c r="I76" t="n">
         <v>206.6423613821681</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K76" t="n">
-        <v>0.08</v>
+        <v>-1.88</v>
       </c>
       <c r="L76" t="n">
         <v>2.47</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>7.96</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="H77" t="n">
-        <v>190.95</v>
+        <v>192.99</v>
       </c>
       <c r="I77" t="n">
         <v>192.5093538378671</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K77" t="n">
-        <v>5.81</v>
+        <v>4.8</v>
       </c>
       <c r="L77" t="n">
         <v>1.23</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>6.6</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H78" t="n">
-        <v>184.3</v>
+        <v>178</v>
       </c>
       <c r="I78" t="n">
         <v>180.2458195557106</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K78" t="n">
-        <v>-4.5</v>
+        <v>-7.77</v>
       </c>
       <c r="L78" t="n">
-        <v>6.73</v>
+        <v>8.93</v>
       </c>
       <c r="M78" t="n">
         <v>1.49</v>
       </c>
       <c r="N78" t="n">
-        <v>2.02</v>
+        <v>3.42</v>
       </c>
       <c r="O78" t="n">
         <v>1.07</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>18</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.9</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.89</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.31</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.38</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100.83</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.14</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.4</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="21">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="25">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.84</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="27">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
